--- a/artfynd/A 35443-2021 artfynd.xlsx
+++ b/artfynd/A 35443-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35443-2021 artfynd.xlsx
+++ b/artfynd/A 35443-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118409</v>
+        <v>115515</v>
       </c>
       <c r="B2" t="n">
-        <v>104840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>107910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,11 @@
           <t>(L.) Schweigg. &amp; Körte</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406984.8760550682</v>
+        <v>406985</v>
       </c>
       <c r="R2" t="n">
-        <v>6167138.873459385</v>
+        <v>6167139</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,36 +749,26 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>M-Lun-0132</t>
+          <t>Arkiv-M-Lun-0036</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inget fynd, Igenlagd åker, gräsmark.</t>
+          <t>2D4b0312, 2D4b0414</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -800,12 +789,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alf Porenius</t>
+          <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
